--- a/methodology/Методика_этап_техника.xlsx
+++ b/methodology/Методика_этап_техника.xlsx
@@ -43748,7 +43748,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>loader, bucket loader big, bucket loader standart, bucket loader standard, wheel loader, forklift standart, forklift standard, forklift giraffe, telehandler, погрузчик</t>
+          <t>loader, bucket loader, bucket loader big, bucket loader standart, bucket loader standard, wheel loader, front loader, forklift, forklift standart, forklift standard, forklift giraffe, telehandler, погрузчик, фронтальный погрузчик</t>
         </is>
       </c>
     </row>
